--- a/Result/profitability/2882.xlsx
+++ b/Result/profitability/2882.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM97"/>
+  <dimension ref="A1:AM98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -663,7 +663,7 @@
         <v>0.85</v>
       </c>
       <c r="M2" t="n">
-        <v>1.575</v>
+        <v>1.58625</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
@@ -766,7 +766,7 @@
         <v>0.08</v>
       </c>
       <c r="M3" t="n">
-        <v>1.3275</v>
+        <v>1.33125</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
@@ -877,7 +877,7 @@
         <v>0.19</v>
       </c>
       <c r="M4" t="n">
-        <v>1.08625</v>
+        <v>1.29125</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
@@ -988,7 +988,7 @@
         <v>1.13</v>
       </c>
       <c r="M5" t="n">
-        <v>1.16375</v>
+        <v>1.16</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
@@ -1099,11 +1099,11 @@
         <v>0.97</v>
       </c>
       <c r="M6" t="n">
-        <v>1.0125</v>
+        <v>1.1925</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
         <v>0.88</v>
       </c>
       <c r="M7" t="n">
-        <v>1.03375</v>
+        <v>1.05875</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="n">
@@ -1337,7 +1337,7 @@
         <v>0.95</v>
       </c>
       <c r="M8" t="n">
-        <v>0.9087499999999999</v>
+        <v>0.9</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="n">
@@ -1456,7 +1456,7 @@
         <v>-0.04</v>
       </c>
       <c r="M9" t="n">
-        <v>0.62625</v>
+        <v>0.6262500000000001</v>
       </c>
       <c r="N9" t="n">
         <v>7.36625</v>
@@ -1940,7 +1940,7 @@
         <v>0.55</v>
       </c>
       <c r="M13" t="n">
-        <v>0.81125</v>
+        <v>0.8112499999999999</v>
       </c>
       <c r="N13" t="n">
         <v>9.266249999999999</v>
@@ -2424,7 +2424,7 @@
         <v>-0.65</v>
       </c>
       <c r="M17" t="n">
-        <v>0.7887500000000001</v>
+        <v>0.78875</v>
       </c>
       <c r="N17" t="n">
         <v>9.828749999999999</v>
@@ -2666,7 +2666,7 @@
         <v>0.12</v>
       </c>
       <c r="M19" t="n">
-        <v>0.63875</v>
+        <v>0.6387499999999999</v>
       </c>
       <c r="N19" t="n">
         <v>10.84375</v>
@@ -11129,6 +11129,113 @@
         <v>114.4</v>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2882</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>115.1Q</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>72538</v>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="n">
+        <v>38392</v>
+      </c>
+      <c r="K98" t="n">
+        <v>31594</v>
+      </c>
+      <c r="L98" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="M98" t="n">
+        <v>1.7375</v>
+      </c>
+      <c r="N98" t="inlineStr"/>
+      <c r="O98" t="n">
+        <v>1</v>
+      </c>
+      <c r="P98" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>0</v>
+      </c>
+      <c r="R98" t="n">
+        <v>0</v>
+      </c>
+      <c r="S98" t="n">
+        <v>0</v>
+      </c>
+      <c r="T98" t="n">
+        <v>0</v>
+      </c>
+      <c r="U98" t="n">
+        <v>1</v>
+      </c>
+      <c r="V98" t="n">
+        <v>115.1</v>
+      </c>
+      <c r="W98" t="n">
+        <v>-0.07000000000000028</v>
+      </c>
+      <c r="X98" t="n">
+        <v>-0.03153153153153165</v>
+      </c>
+      <c r="Y98" t="inlineStr"/>
+      <c r="Z98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA98" t="n">
+        <v>-0.03000000000000025</v>
+      </c>
+      <c r="AB98" t="n">
+        <v>-0.0137614678899084</v>
+      </c>
+      <c r="AC98" t="inlineStr"/>
+      <c r="AD98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ98" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK98" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL98" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM98" t="n">
+        <v>115.1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
